--- a/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_40_P90.xlsx
+++ b/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_40_P90.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55C6643A-F5E7-4F5A-B540-B05D4254EE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE001EFF-79F7-44BB-9046-E4A3D61847AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,13 +681,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH06,S02aH02,S04aH02,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S01aH03,S01aH06,S02aH03,S01aH02,S04aH04,S03aH04,S03aH02,S03aH03,S02aH04,S02aH05,S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</t>
+    <t>S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S04aH02,S01aH02,S04aH04,S02aH04,S02aH05,S04aH06,S03aH03,S01aH04,S01aH07,S02aH07,S02aH02,S01aH03,S01aH06,S02aH03,S03aH04,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH05,S04aH08</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S04aH08,S01aH10,S03aH02,S01aH09,S01aH01,S04aH01,S01aH08,S02aH08,S02aH09,S04aH09,S04aH02,S02aH02,S04aH10,S03aH08,S03aH10,S02aH01,S02aH10,S03aH09,S01aH02</t>
+    <t>S03aH09,S02aH01,S02aH10,S01aH10,S03aH02,S01aH08,S02aH08,S04aH08,S03aH08,S03aH10,S02aH02,S04aH10,S01aH09,S03aH01,S01aH01,S04aH01,S02aH09,S04aH09,S04aH02,S01aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH01,S04aH08,S01aH10,S03aH02,S01aH09,S01aH01,S04aH01,S01aH08,S02aH08,S02aH09,S04aH09,S04aH02,S02aH02,S04aH10,S03aH08,S03aH10,S02aH01,S02aH10,S03aH09,S01aH02</v>
+        <v>S03aH09,S02aH01,S02aH10,S01aH10,S03aH02,S01aH08,S02aH08,S04aH08,S03aH08,S03aH10,S02aH02,S04aH10,S01aH09,S03aH01,S01aH01,S04aH01,S02aH09,S04aH09,S04aH02,S01aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH06,S02aH02,S04aH02,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S01aH03,S01aH06,S02aH03,S01aH02,S04aH04,S03aH04,S03aH02,S03aH03,S02aH04,S02aH05,S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</v>
+        <v>S02aH06,S03aH05,S03aH08,S04aH07,S04aH03,S04aH02,S01aH02,S04aH04,S02aH04,S02aH05,S04aH06,S03aH03,S01aH04,S01aH07,S02aH07,S02aH02,S01aH03,S01aH06,S02aH03,S03aH04,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S04aH05,S04aH08</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1410,7 +1410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4B8C060-4752-411D-9675-1DD9D0F43F61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42FF9785-CDB4-4441-AD4B-FDD02AAC63DC}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1548,7 +1548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05EBF34-746B-4BAA-9479-7E88CDFDFEFC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A002A85C-68E7-495C-9087-7CDBD6746731}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27210,7 +27210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99DC8081-A9B9-4992-8E31-92750087E8DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD284F36-53F7-47CE-9CDB-0E187B154977}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41663,7 +41663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85A1EB80-6976-40A3-B61D-721E47F7EAD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32BDF00D-DDC5-43C1-B77B-0A992B69C385}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -42253,7 +42253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F70CC02-44B7-4618-8D33-2BB0FC8DE060}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA13259B-9093-4E01-A095-434C00630F0E}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43160,7 +43160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EF7D34-1ED1-41C8-85FF-4780731EB6C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{797A1B51-C889-44E4-A784-29F691D9D772}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43627,7 +43627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E611A194-46E1-4BBF-859A-A126366380D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFD9C411-B78B-4753-B03B-33D42895433C}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43701,7 +43701,7 @@
         <v>45</v>
       </c>
       <c r="D14">
-        <v>0.19110000000000002</v>
+        <v>0.19109999999999996</v>
       </c>
       <c r="E14" t="s">
         <v>221</v>
@@ -43785,7 +43785,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>0.23149999999999996</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="E20" t="s">
         <v>221</v>
@@ -43799,7 +43799,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>0.12036666666666668</v>
+        <v>0.12036666666666666</v>
       </c>
       <c r="E21" t="s">
         <v>221</v>
@@ -43953,7 +43953,7 @@
         <v>41</v>
       </c>
       <c r="D32">
-        <v>0.33896666666666669</v>
+        <v>0.33896666666666664</v>
       </c>
       <c r="E32" t="s">
         <v>221</v>
@@ -43981,7 +43981,7 @@
         <v>45</v>
       </c>
       <c r="D34">
-        <v>0.24309999999999998</v>
+        <v>0.24310000000000001</v>
       </c>
       <c r="E34" t="s">
         <v>221</v>
@@ -44037,7 +44037,7 @@
         <v>45</v>
       </c>
       <c r="D38">
-        <v>0.2779666666666667</v>
+        <v>0.27796666666666664</v>
       </c>
       <c r="E38" t="s">
         <v>221</v>
@@ -44135,7 +44135,7 @@
         <v>43</v>
       </c>
       <c r="D45">
-        <v>0.24373333333333333</v>
+        <v>0.24373333333333336</v>
       </c>
       <c r="E45" t="s">
         <v>221</v>
@@ -44191,7 +44191,7 @@
         <v>43</v>
       </c>
       <c r="D49">
-        <v>0.24983333333333335</v>
+        <v>0.24983333333333332</v>
       </c>
       <c r="E49" t="s">
         <v>221</v>
@@ -44373,7 +44373,7 @@
         <v>45</v>
       </c>
       <c r="D62">
-        <v>0.30070000000000002</v>
+        <v>0.30069999999999997</v>
       </c>
       <c r="E62" t="s">
         <v>221</v>
@@ -44457,7 +44457,7 @@
         <v>41</v>
       </c>
       <c r="D68">
-        <v>0.41579999999999995</v>
+        <v>0.4158</v>
       </c>
       <c r="E68" t="s">
         <v>221</v>
@@ -44471,7 +44471,7 @@
         <v>43</v>
       </c>
       <c r="D69">
-        <v>0.23163333333333333</v>
+        <v>0.23163333333333336</v>
       </c>
       <c r="E69" t="s">
         <v>221</v>
@@ -44527,7 +44527,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.21283333333333332</v>
+        <v>0.21283333333333335</v>
       </c>
       <c r="E73" t="s">
         <v>221</v>
@@ -44653,7 +44653,7 @@
         <v>45</v>
       </c>
       <c r="D82">
-        <v>0.20663333333333334</v>
+        <v>0.20663333333333331</v>
       </c>
       <c r="E82" t="s">
         <v>221</v>
@@ -44709,7 +44709,7 @@
         <v>45</v>
       </c>
       <c r="D86">
-        <v>0.21799999999999997</v>
+        <v>0.218</v>
       </c>
       <c r="E86" t="s">
         <v>221</v>
@@ -44737,7 +44737,7 @@
         <v>41</v>
       </c>
       <c r="D88">
-        <v>0.32750000000000001</v>
+        <v>0.32750000000000007</v>
       </c>
       <c r="E88" t="s">
         <v>221</v>
@@ -44751,7 +44751,7 @@
         <v>43</v>
       </c>
       <c r="D89">
-        <v>0.20476666666666668</v>
+        <v>0.20476666666666665</v>
       </c>
       <c r="E89" t="s">
         <v>221</v>
@@ -44807,7 +44807,7 @@
         <v>43</v>
       </c>
       <c r="D93">
-        <v>0.21499999999999997</v>
+        <v>0.215</v>
       </c>
       <c r="E93" t="s">
         <v>221</v>
@@ -44821,7 +44821,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.22556666666666667</v>
+        <v>0.22556666666666669</v>
       </c>
       <c r="E94" t="s">
         <v>221</v>
@@ -44877,7 +44877,7 @@
         <v>45</v>
       </c>
       <c r="D98">
-        <v>0.21693333333333334</v>
+        <v>0.21693333333333331</v>
       </c>
       <c r="E98" t="s">
         <v>221</v>
@@ -45017,7 +45017,7 @@
         <v>41</v>
       </c>
       <c r="D108">
-        <v>0.29843333333333338</v>
+        <v>0.29843333333333333</v>
       </c>
       <c r="E108" t="s">
         <v>221</v>
@@ -45045,7 +45045,7 @@
         <v>45</v>
       </c>
       <c r="D110">
-        <v>0.20140000000000002</v>
+        <v>0.2014</v>
       </c>
       <c r="E110" t="s">
         <v>221</v>
@@ -45143,7 +45143,7 @@
         <v>43</v>
       </c>
       <c r="D117">
-        <v>0.20376666666666668</v>
+        <v>0.20376666666666665</v>
       </c>
       <c r="E117" t="s">
         <v>221</v>
